--- a/data/trans_dic/P16A20_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A20_2023-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alteración del tiroides últimas 2 semanas</t>
+          <t>Población que ha consumido medicamentos para la alteración del tiroides en las últimas 2 semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,44</t>
+          <t>0,0; 5,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,47</t>
+          <t>1,33; 7,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,62</t>
+          <t>1,13; 5,18</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,74</t>
+          <t>1,51; 4,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,79</t>
+          <t>0,97; 2,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,47</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,08</t>
+          <t>0,23; 2,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,97</t>
+          <t>4,78; 8,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,46</t>
+          <t>2,67; 4,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,34</t>
+          <t>0,37; 2,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,59</t>
+          <t>7,03; 11,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,13</t>
+          <t>2,66; 6,12</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,57</t>
+          <t>0,68; 2,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 15,24</t>
+          <t>10,86; 15,42</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,01; 8,42</t>
+          <t>5,97; 8,51</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,04</t>
+          <t>1,35; 3,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 75,42</t>
+          <t>11,13; 77,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 64,9</t>
+          <t>6,93; 60,59</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,14</t>
+          <t>1,11; 4,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,81; 12,0</t>
+          <t>7,86; 12,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 4,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 8,04</t>
+          <t>5,34; 8,4</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,81</t>
+          <t>0,91; 1,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,89; 28,24</t>
+          <t>7,87; 32,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 17,33</t>
+          <t>4,53; 17,53</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para la alteración del tiroides últimas 2 semanas</t>
+          <t>Población que ha consumido medicamentos para la alteración del tiroides en las últimas 2 semanas (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1900</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2025</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 21779</t>
+          <t>0; 22797</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1836</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1867</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4334; 23408</t>
+          <t>4177; 23672</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1928</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 1962</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6723; 32964</t>
+          <t>8074; 36925</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1971</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1976</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7310</t>
+          <t>0; 7280</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2031</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2011</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1852</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7413; 24225</t>
+          <t>7706; 25179</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2024</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 1988</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1924</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8973; 26103</t>
+          <t>9107; 26200</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2020</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1996</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1079; 11151</t>
+          <t>1231; 10886</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2003</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2054</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1884</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25966; 43219</t>
+          <t>25938; 44652</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 2016</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1950</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29045; 48168</t>
+          <t>28838; 50287</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2158</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2113</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3586; 20768</t>
+          <t>3275; 20540</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1984</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2225</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2048</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48953; 82632</t>
+          <t>50091; 81310</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2039</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 2188</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2088</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44507; 98091</t>
+          <t>42574; 97922</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1860</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2073</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2155</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4003; 14412</t>
+          <t>3798; 14336</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 1930</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2174</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2211</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59839; 82919</t>
+          <t>59084; 83946</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 1905</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 2130</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 2187</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>66324; 93014</t>
+          <t>65956; 94021</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1856</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1930</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1939</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4482; 14885</t>
+          <t>4987; 14657</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1732</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2003</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2060</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>68273; 458550</t>
+          <t>67686; 468388</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1832</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 2012</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>67692; 633501</t>
+          <t>67671; 591473</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1769</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1932</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1567</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3033; 11695</t>
+          <t>3128; 11470</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2117</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2076</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2277</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>33170; 50975</t>
+          <t>33390; 51110</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 1983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 2086</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 1879</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>37521; 56881</t>
+          <t>37771; 59398</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2013</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2032</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>30900; 62529</t>
+          <t>31327; 61801</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 1969</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 1948</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>288444; 1032918</t>
+          <t>287815; 1179965</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0; 1982</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 1997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>323603; 1233134</t>
+          <t>322547; 1247335</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A20_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A20_2023-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,7</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,56</t>
+          <t>1,71; 7,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,18</t>
+          <t>1,09; 4,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,92</t>
+          <t>2,12; 5,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,8</t>
+          <t>1,12; 2,95</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,03</t>
+          <t>0,18; 1,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 8,23</t>
+          <t>4,51; 7,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,66</t>
+          <t>2,55; 4,26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,31</t>
+          <t>0,73; 2,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 11,41</t>
+          <t>7,05; 10,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,12</t>
+          <t>4,2; 6,17</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,56</t>
+          <t>0,83; 2,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,86; 15,42</t>
+          <t>11,45; 15,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,51</t>
+          <t>6,31; 8,77</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,98</t>
+          <t>1,19; 3,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,13; 77,04</t>
+          <t>10,23; 14,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 60,59</t>
+          <t>6,29; 9,0</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,06</t>
+          <t>1,08; 3,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,86; 12,03</t>
+          <t>7,9; 12,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,4</t>
+          <t>5,56; 8,47</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,79</t>
+          <t>0,97; 1,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,87; 32,27</t>
+          <t>7,6; 9,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,53; 17,53</t>
+          <t>4,51; 5,36</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>18346</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 22797</t>
+          <t>0; 24052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4177; 23672</t>
+          <t>6211; 27993</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8074; 36925</t>
+          <t>8397; 35687</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1361</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16242</t>
+          <t>18993</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7280</t>
+          <t>0; 6942</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7706; 25179</t>
+          <t>10619; 28127</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9107; 26200</t>
+          <t>10956; 28893</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>37273</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>37561</t>
+          <t>41525</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1231; 10886</t>
+          <t>1114; 10118</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25938; 44652</t>
+          <t>28055; 48373</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28838; 50287</t>
+          <t>31752; 52977</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>62628</t>
+          <t>62303</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73543</t>
+          <t>73048</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3275; 20540</t>
+          <t>5117; 18558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50091; 81310</t>
+          <t>51939; 75024</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>42574; 97922</t>
+          <t>60420; 88702</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8251</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>70705</t>
+          <t>80871</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>78957</t>
+          <t>90615</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3798; 14336</t>
+          <t>5047; 16664</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59084; 83946</t>
+          <t>69462; 96701</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>65956; 94021</t>
+          <t>76692; 106587</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>252918</t>
+          <t>54470</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>261556</t>
+          <t>63832</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4987; 14657</t>
+          <t>4858; 15671</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>67686; 468388</t>
+          <t>44894; 65747</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>67671; 591473</t>
+          <t>53180; 76095</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>41047</t>
+          <t>45288</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>47054</t>
+          <t>52104</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3128; 11470</t>
+          <t>3353; 12177</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>33390; 51110</t>
+          <t>36625; 55816</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>37771; 59398</t>
+          <t>42983; 65532</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>47404</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>486253</t>
+          <t>311059</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>531377</t>
+          <t>358463</t>
         </is>
       </c>
     </row>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>31327; 61801</t>
+          <t>34212; 63640</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>287815; 1179965</t>
+          <t>283571; 344144</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>322547; 1247335</t>
+          <t>327281; 389166</t>
         </is>
       </c>
     </row>
